--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CBI ELCHE.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CBI ELCHE.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6479</v>
+        <v>3.4886</v>
       </c>
       <c r="E2" t="n">
-        <v>3.73</v>
+        <v>3.8768</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.3882</v>
       </c>
       <c r="G2" t="n">
-        <v>0.615</v>
+        <v>0.4944</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0172</v>
+        <v>-1.0695</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6322</v>
+        <v>1.5638</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6815</v>
+        <v>1.7455</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.8134</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.9321</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0665</v>
+        <v>-1.2511</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7787</v>
+        <v>-1.8828</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7123</v>
+        <v>0.6317</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S2" t="n">
-        <v>1.593</v>
+        <v>1.5395</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0094</v>
+        <v>1.0134</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5837</v>
+        <v>0.5261</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1606</v>
+        <v>-0.1032</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0392</v>
+        <v>1.1179</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1131</v>
+        <v>2.2703</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2762</v>
+        <v>3.6441</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1631</v>
+        <v>-1.3737</v>
       </c>
       <c r="G3" t="n">
-        <v>5.7195</v>
+        <v>5.783</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3706</v>
+        <v>2.4211</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3489</v>
+        <v>3.3619</v>
       </c>
       <c r="J3" t="n">
-        <v>7.1422</v>
+        <v>7.3368</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4208</v>
+        <v>3.5434</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7214</v>
+        <v>3.7934</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4227</v>
+        <v>-1.5538</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0502</v>
+        <v>-1.1223</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3725</v>
+        <v>-0.4315</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0454</v>
+        <v>-0.0463</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0243</v>
+        <v>-0.0064</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.021</v>
+        <v>-0.0399</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.3604</v>
+        <v>-1.3242</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.8408</v>
+        <v>-0.7653</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2146</v>
+        <v>1.3636</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4176</v>
+        <v>0.8321</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7971</v>
+        <v>0.5316</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1629</v>
+        <v>4.2899</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1858</v>
+        <v>1.2552</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9771</v>
+        <v>3.0347</v>
       </c>
       <c r="J4" t="n">
-        <v>4.094</v>
+        <v>4.3871</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3647</v>
+        <v>2.5223</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7293</v>
+        <v>1.8648</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0689</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1789</v>
+        <v>-1.2671</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2478</v>
+        <v>1.1699</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.6005</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1684</v>
+        <v>-1.1405</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4755</v>
+        <v>-0.4393</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6928</v>
+        <v>-0.7013</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1795</v>
+        <v>-0.2279</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1795</v>
+        <v>-0.2279</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3857</v>
+        <v>0.4064</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3653</v>
+        <v>0.4826</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0204</v>
+        <v>-0.0762</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4375</v>
+        <v>0.4589</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9935</v>
+        <v>-0.9821</v>
       </c>
       <c r="I5" t="n">
-        <v>1.431</v>
+        <v>1.4411</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9454</v>
+        <v>1.0391</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3363</v>
+        <v>-0.2822</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2817</v>
+        <v>1.3213</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5079</v>
+        <v>-0.5802</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6573</v>
+        <v>-0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1493</v>
+        <v>0.1198</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0521</v>
+        <v>-1.0262</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5565</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.472</v>
+        <v>-0.4697</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -886,10 +886,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -904,10 +904,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1356</v>
+        <v>-0.1329</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1356</v>
+        <v>-0.1329</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8397</v>
+        <v>-0.9906</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7695</v>
+        <v>0.9398</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6092</v>
+        <v>-1.9304</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6206</v>
+        <v>-1.751</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.4898</v>
+        <v>-2.6002</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8692</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3105</v>
+        <v>-0.1973</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3181</v>
+        <v>-0.295</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0076</v>
+        <v>0.0978</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3101</v>
+        <v>-1.5537</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.1717</v>
+        <v>-2.3052</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8616</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0196</v>
+        <v>-0.9922</v>
       </c>
       <c r="T7" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.1108</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0999</v>
+        <v>-1.103</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1289</v>
+        <v>-1.9769</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4297</v>
+        <v>0.037</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6992</v>
+        <v>-2.0139</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3373</v>
+        <v>1.3752</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0244</v>
+        <v>0.0313</v>
       </c>
       <c r="I8" t="n">
-        <v>1.313</v>
+        <v>1.3439</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3762</v>
+        <v>2.6631</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9249</v>
+        <v>2.0707</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4514</v>
+        <v>0.5924</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0389</v>
+        <v>-1.2879</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.9005</v>
+        <v>-2.0394</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8616</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.8657</v>
+        <v>-2.7942</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.4047</v>
+        <v>-1.3419</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.4611</v>
+        <v>-1.4523</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6982</v>
+        <v>-3.7787</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7321</v>
+        <v>-0.6276</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9661</v>
+        <v>-3.1511</v>
       </c>
       <c r="G9" t="n">
-        <v>0.483</v>
+        <v>0.433</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4312</v>
+        <v>0.43</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0518</v>
+        <v>0.003</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8416</v>
+        <v>0.8934</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6816</v>
+        <v>0.7313</v>
       </c>
       <c r="L9" t="n">
-        <v>0.16</v>
+        <v>0.1621</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3586</v>
+        <v>-0.4604</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2505</v>
+        <v>-0.3013</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1082</v>
+        <v>-0.1591</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5816</v>
+        <v>-0.5748</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3734</v>
+        <v>-0.3525</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2082</v>
+        <v>-0.2223</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.9994</v>
+        <v>-3.0526</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.9994</v>
+        <v>-3.0526</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8992</v>
+        <v>-4.9464</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5069</v>
+        <v>-3.2792</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3924</v>
+        <v>-1.6673</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.8464</v>
+        <v>-2.874</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.645</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1997</v>
+        <v>-2.229</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1867</v>
+        <v>-2.0268</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3253</v>
+        <v>0.4286</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.512</v>
+        <v>-2.4554</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6597</v>
+        <v>-0.8472</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9721</v>
+        <v>-1.0736</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3123</v>
+        <v>0.2264</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S10" t="n">
         <v>0.207</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.8897</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6735</v>
+        <v>-0.6827</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2047</v>
+        <v>-4.1637</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8899</v>
+        <v>5.9056</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.0946</v>
+        <v>-10.0692</v>
       </c>
       <c r="G11" t="n">
-        <v>8.4238</v>
+        <v>8.3423</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9995999999999998</v>
+        <v>-1.0263</v>
       </c>
       <c r="I11" t="n">
-        <v>9.423499999999999</v>
+        <v>9.3687</v>
       </c>
       <c r="J11" t="n">
-        <v>14.5837</v>
+        <v>15.8409</v>
       </c>
       <c r="K11" t="n">
-        <v>8.824499999999999</v>
+        <v>9.532499999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>5.7593</v>
+        <v>6.3085</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.1599</v>
+        <v>-7.498600000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-9.824299999999999</v>
+        <v>-10.5588</v>
       </c>
       <c r="O11" t="n">
-        <v>3.664200000000001</v>
+        <v>3.0602</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0005</v>
+        <v>-1.9473</v>
       </c>
       <c r="Q11" t="n">
-        <v>-13.0037</v>
+        <v>-12.6578</v>
       </c>
       <c r="R11" t="n">
-        <v>11.0033</v>
+        <v>10.7106</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.0684</v>
+        <v>-4.960599999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8878999999999998</v>
+        <v>-0.6827</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.1804</v>
+        <v>-4.278</v>
       </c>
       <c r="V11" t="n">
-        <v>-5.559600000000001</v>
+        <v>-5.5979</v>
       </c>
       <c r="W11" t="n">
-        <v>3.1979</v>
+        <v>3.4053</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.7575</v>
+        <v>-9.003299999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CBI ELCHE.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CBI ELCHE.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4886</v>
+        <v>2.6277</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8768</v>
+        <v>3.2787</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3882</v>
+        <v>-0.6511</v>
       </c>
       <c r="G2" t="n">
         <v>0.4944</v>
@@ -610,13 +610,13 @@
         <v>1.5579</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5395</v>
+        <v>0.6786</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0134</v>
+        <v>0.4153</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5261</v>
+        <v>0.2632</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1032</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2703</v>
+        <v>2.4805</v>
       </c>
       <c r="E3" t="n">
         <v>3.6441</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3737</v>
+        <v>-1.1636</v>
       </c>
       <c r="G3" t="n">
         <v>5.783</v>
@@ -688,13 +688,13 @@
         <v>0.7789</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0463</v>
+        <v>0.1638</v>
       </c>
       <c r="T3" t="n">
         <v>-0.0064</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0399</v>
+        <v>0.1703</v>
       </c>
       <c r="V3" t="n">
         <v>-1.3242</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3636</v>
+        <v>2.117</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8321</v>
+        <v>1.1311</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5316</v>
+        <v>0.9859</v>
       </c>
       <c r="G4" t="n">
         <v>4.2899</v>
@@ -766,13 +766,13 @@
         <v>1.5579</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1405</v>
+        <v>-0.3872</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4393</v>
+        <v>-0.1403</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7013</v>
+        <v>-0.2469</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2279</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4064</v>
+        <v>0.9991</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4826</v>
+        <v>0.7816</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0762</v>
+        <v>0.2174</v>
       </c>
       <c r="G5" t="n">
         <v>0.4589</v>
@@ -844,13 +844,13 @@
         <v>0.9737</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0262</v>
+        <v>-0.4335</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5565</v>
+        <v>-0.2575</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4697</v>
+        <v>-0.1761</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.1329</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.1329</v>
       </c>
       <c r="G6" t="n">
         <v>0.1329</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1329</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1329</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GOMEZ-ARRONES MORGADO</t>
+          <t>D. SALVADOR ESCUDER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9906</v>
+        <v>-0.0257</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9398</v>
+        <v>0.9341</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9304</v>
+        <v>-0.9599</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.751</v>
+        <v>1.3752</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.6002</v>
+        <v>0.0313</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8493000000000001</v>
+        <v>1.3439</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1973</v>
+        <v>2.6631</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.295</v>
+        <v>2.0707</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0978</v>
+        <v>0.5924</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5537</v>
+        <v>-1.2879</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.3052</v>
+        <v>-2.0394</v>
       </c>
       <c r="O7" t="n">
         <v>0.7514999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7526</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1947</v>
+        <v>-3.1158</v>
       </c>
       <c r="R7" t="n">
         <v>1.9474</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9922</v>
+        <v>-0.8431</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1108</v>
+        <v>-0.4448</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.103</v>
+        <v>-0.3983</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2211</v>
+        <v>1.8316</v>
       </c>
       <c r="X7" t="n">
         <v>-1.2211</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. SALVADOR ESCUDER</t>
+          <t>A. GOMEZ-ARRONES MORGADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9769</v>
+        <v>-0.3414</v>
       </c>
       <c r="E8" t="n">
-        <v>0.037</v>
+        <v>0.9398</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0139</v>
+        <v>-1.2813</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3752</v>
+        <v>-1.751</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0313</v>
+        <v>-2.6002</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3439</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6631</v>
+        <v>-0.1973</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0707</v>
+        <v>-0.295</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5924</v>
+        <v>0.0978</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2879</v>
+        <v>-1.5537</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.0394</v>
+        <v>-2.3052</v>
       </c>
       <c r="O8" t="n">
         <v>0.7514999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1684</v>
+        <v>1.7526</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1158</v>
+        <v>-0.1947</v>
       </c>
       <c r="R8" t="n">
         <v>1.9474</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.7942</v>
+        <v>-0.3431</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3419</v>
+        <v>0.1108</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.4523</v>
+        <v>-0.4539</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6105</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8316</v>
+        <v>1.2211</v>
       </c>
       <c r="X8" t="n">
         <v>-1.2211</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7787</v>
+        <v>-3.5029</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6276</v>
+        <v>-0.5279</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.1511</v>
+        <v>-2.975</v>
       </c>
       <c r="G9" t="n">
         <v>0.433</v>
@@ -1156,13 +1156,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5748</v>
+        <v>-0.299</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3525</v>
+        <v>-0.2529</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2223</v>
+        <v>-0.0462</v>
       </c>
       <c r="V9" t="n">
         <v>-3.0526</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9464</v>
+        <v>-5.3281</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2792</v>
+        <v>-4.2759</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6673</v>
+        <v>-1.0522</v>
       </c>
       <c r="G10" t="n">
         <v>-2.874</v>
@@ -1234,13 +1234,13 @@
         <v>1.3632</v>
       </c>
       <c r="S10" t="n">
-        <v>0.207</v>
+        <v>-0.1747</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8897</v>
+        <v>-0.107</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6827</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5005</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1637</v>
+        <v>-0.8409000000000004</v>
       </c>
       <c r="E11" t="n">
         <v>5.9056</v>
       </c>
       <c r="F11" t="n">
-        <v>-10.0692</v>
+        <v>-6.7469</v>
       </c>
       <c r="G11" t="n">
         <v>8.3423</v>
@@ -1312,13 +1312,13 @@
         <v>10.7106</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.960599999999999</v>
+        <v>-1.6382</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6827</v>
+        <v>-0.6828000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.278</v>
+        <v>-0.9555</v>
       </c>
       <c r="V11" t="n">
         <v>-5.5979</v>
